--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_622_Azores_Isl_Portugal.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_622_Azores_Isl_Portugal.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rb3b6f0a216874055"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R03724f02fcc843d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Red8de1aadcb64ae8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R106e195b37074a7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rb39c49d6c4294764"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R8baafbfbc3be4d76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rcf2e2a9af5fd4637"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R9aaf3cd4216a46b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rd2ca1a32e1934dbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rd5d402a4364348b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R8d5e38201f2e4334"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R82833d6023864a40"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ622CommercialTable" displayName="EEZ622CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ622CommercialTable" displayName="EEZ622CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ622FunctionalTable" displayName="EEZ622FunctionalTable" ref="A1:O25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O25"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ622FunctionalTable" displayName="EEZ622FunctionalTable" ref="A1:E25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E25"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ622ValidationTable" displayName="EEZ622ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ622ValidationTable" displayName="EEZ622ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -9538,7 +9492,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra074610f47664bdb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re80b74eca8554393"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9548,20 +9502,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -9569,660 +9513,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>236.61480321599998</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.9496146018527982</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>890.4603821570536</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>236.61480321599998</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1056.0760851787572</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$133,A2,'Species'!$U$2:$U$133))</x:f>
-        <x:v>249883.23507569527</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.9496146018527982</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>890.4603821570536</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>210696.10809573537</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>39187.126979959896</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.1859888506443326</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.18598885064433265</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>37.971743209</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.9953583795413365</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>98.93691847393625</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>37.971743209</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>131.03109964285028</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$133,A3,'Species'!$U$2:$U$133))</x:f>
-        <x:v>4975.479268031203</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.9953583795413365</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>98.93691847393625</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>3756.8072621820756</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>1218.6720058491273</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.3243903455247483</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.3243903455247483</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>0.25</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.57</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>371.5352290971724</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>371.5352290971724</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$133,A4,'Species'!$U$2:$U$133))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>92.8838072742931</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.57</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>371.5352290971724</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>92.8838072742931</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>191.082329868</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.06</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>114.81536214968828</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>191.082329868</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>114.8153621496883</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$133,A5,'Species'!$U$2:$U$133))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>21939.18690420062</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.06</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>114.81536214968828</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>21939.18690420062</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>1486.133848118</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.0888931199884833</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>12.271371951364006</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>1486.133848118</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>12.325787272332953</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$133,A6,'Species'!$U$2:$U$133))</x:f>
-        <x:v>18317.76967011604</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.0888931199884833</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>12.271371951364006</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>18236.901219767882</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>80.86845034815633</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0044343306669061</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.004434330666906228</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>5926.339917572401</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.4288236064468127</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>268.4253984493641</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>5926.339917572401</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>432.34677814948606</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$133,A7,'Species'!$U$2:$U$133))</x:f>
-        <x:v>2562233.9695811183</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.4288236064468127</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>268.4253984493641</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>1590780.1537207433</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>971453.8158603751</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.6106776059458627</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.6106776059458627</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>4895.297134459801</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.5800582272467953</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>380.2403729431343</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>4895.297134459801</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>683.1579678472959</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$133,A8,'Species'!$U$2:$U$133))</x:f>
-        <x:v>3344261.2423862484</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.5800582272467953</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>380.2403729431343</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>1861389.6080744513</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>1482871.634311797</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.7966476378074232</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.7966476378074233</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>0.16585376599999999</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.6665782888523615</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>464.0644378278334</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>0.16585376599999999</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>465.04638111287903</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$133,A9,'Species'!$U$2:$U$133))</x:f>
-        <x:v>77.12969367224225</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.6665782888523615</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>464.0644378278334</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>76.96683468041903</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0.16285899182322794</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0021159632262318</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.0021159632262317857</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>460.359008617</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.7611039902447154</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>576.904584573874</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>460.359008617</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>639.4742655210459</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$133,A10,'Species'!$U$2:$U$133))</x:f>
-        <x:v>294387.73891135294</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.7611039902447154</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>576.904584573874</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>265583.2226210309</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>28804.516290322063</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.1084575900768556</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.10845759007685565</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>2761.8912458044</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.35375453974571</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2258.1591134758196</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>2761.8912458044</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2286.611700380633</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$133,A11,'Species'!$U$2:$U$133))</x:f>
-        <x:v>6315372.837835184</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.35375453974571</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2258.1591134758196</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>6236789.887142291</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>78582.950692893</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.012599903494408</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.01259990349440806</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>5198.9294116562005</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.4511292540275855</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2825.7208362876204</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>5198.9294116562005</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2839.986663895787</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$133,A12,'Species'!$U$2:$U$133))</x:f>
-        <x:v>14764890.195639178</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.4511292540275855</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2825.7208362876204</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>14690723.164905464</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>74167.03073371388</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0050485622730194</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.0050485622730194</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e55ff31b099410d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44775bcbcf304ac9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10232,20 +9747,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -10253,1362 +9758,478 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>0.5600621</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.147167567667943</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1403.3550689713586</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>0.5600621</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1785.6668500448172</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$133,A2,'Species'!$U$2:$U$133))</x:f>
-        <x:v>1000.0843259364855</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.147167567667943</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1403.3550689713586</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>785.965986973744</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>214.11833896274152</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.2724269784080293</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.2724269784080292</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>241.56027991000002</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.838388801344555</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>689.2690871085152</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>241.56027991000002</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>723.6733262152864</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$133,A3,'Species'!$U$2:$U$133))</x:f>
-        <x:v>174810.73124396533</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.838388801344555</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>689.2690871085152</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>166500.03361524313</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>8310.697628722206</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0499140897948824</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.04991408979488254</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>21.5308274499</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.284382226171454</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1924.7850028956382</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>21.5308274499</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1987.4076175177618</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$133,A4,'Species'!$U$2:$U$133))</x:f>
-        <x:v>42790.530485391784</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.284382226171454</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1924.7850028956382</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>41442.21377550125</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1348.3167098905324</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0325348620900072</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.03253486209000726</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>106.5107225668</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.448432636123361</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2808.229751495652</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>106.5107225668</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2858.127411009451</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$133,A5,'Species'!$U$2:$U$133))</x:f>
-        <x:v>304421.215734594</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.448432636123361</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2808.229751495652</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>299106.5799653871</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>5314.635769206856</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.017768367950387</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.017768367950387016</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>396.384191873</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.308045894809629</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2032.5717950761398</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>396.384191873</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2035.2726277166214</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$133,A6,'Species'!$U$2:$U$133))</x:f>
-        <x:v>806749.8957786902</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.308045894809629</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2032.5717950761398</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>805679.3284151086</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>1070.5673635816202</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0013287760102862</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.0013287760102863577</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>5252.150617281701</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.45023056964045</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2819.879625551536</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>5252.150617281701</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2834.4596065019196</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$133,A7,'Species'!$U$2:$U$133))</x:f>
-        <x:v>14887008.771949103</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.45023056964045</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2819.879625551536</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>14810432.51600059</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>76576.25594851375</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.005170426715478</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.005170426715478017</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>2.5169646720000003</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.8918964890103944</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>779.6442657314034</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>2.5169646720000003</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1216.0585086651818</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$133,A8,'Species'!$U$2:$U$133))</x:f>
-        <x:v>3060.776305395269</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.8918964890103944</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>779.6442657314034</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>1962.3370735733229</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>1098.4392318219461</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.5597607294967628</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.5597607294967629</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>415.457984109</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.0738916236469915</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1185.472881503755</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>415.457984109</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1369.280205486001</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$133,A9,'Species'!$U$2:$U$133))</x:f>
-        <x:v>568878.3938515713</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.0738916236469915</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1185.472881503755</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>492514.17356543744</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>76364.22028613382</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1550497922391014</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.15504979223910142</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>2743.9961284864003</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.355294911034322</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>2266.1826541182254</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>2743.9961284864003</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2292.3892105259933</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$133,A10,'Species'!$U$2:$U$133))</x:f>
-        <x:v>6290307.118667321</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.355294911034322</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>2266.1826541182254</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>6218396.429343445</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>71910.68932387605</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.011564185419981</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.011564185419981108</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>17.711743209</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.325120430661163</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>211.4075195514331</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>17.711743209</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>221.6761666068784</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$133,A11,'Species'!$U$2:$U$133))</x:f>
-        <x:v>3926.271338496532</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.325120430661163</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>211.4075195514331</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>3744.3956987466304</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>181.87563974990144</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0485727616370195</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.048572761637019575</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>434.46575928299995</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.842573069456992</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>695.9420361537192</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>434.46575928299995</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>852.6283720527607</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$133,A12,'Species'!$U$2:$U$133))</x:f>
-        <x:v>370437.83305013087</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.842573069456992</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>695.9420361537192</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>302362.9851544826</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>68074.84789564827</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.2251427960365837</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.22514279603658374</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>133.5362579374</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.752940345203668</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>566.1615156125292</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>133.5362579374</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>568.1907232407058</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$133,A13,'Species'!$U$2:$U$133))</x:f>
-        <x:v>75874.06297630873</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.752940345203668</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>566.1615156125292</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>75603.09018306402</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>270.9727932447131</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.003584149703254</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.003584149703253984</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>4172.318878450101</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.6205662559933267</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>417.4132742032303</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>4172.318878450101</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>685.8696690254053</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$133,A14,'Species'!$U$2:$U$133))</x:f>
-        <x:v>2861666.968231021</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.6205662559933267</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>417.4132742032303</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>1741581.2840738061</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>1120085.6841572148</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.6431429267183988</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.6431429267183988</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>5075.6425014869</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.270813241053661</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>186.55772671710483</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>5075.6425014869</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>188.41052743242685</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$133,A15,'Species'!$U$2:$U$133))</x:f>
-        <x:v>956304.4807635893</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.270813241053661</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>186.55772671710483</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>946900.3267061154</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>9404.154057473876</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.00993151421775</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.00993151421774997</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>10.8156335166</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.938248954140141</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>867.4589937995361</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>10.8156335166</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>1588.7482380505246</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$133,A16,'Species'!$U$2:$U$133))</x:f>
-        <x:v>17183.31869289845</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.938248954140141</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>867.4589937995361</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>9382.118567614374</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>7801.200125284076</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.8314966464197773</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.8314966464197773</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>421.40268408699995</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.1642601504487318</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>145.96883788517155</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>421.40268408699995</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>309.18184203893526</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$133,A17,'Species'!$U$2:$U$133))</x:f>
-        <x:v>130290.05810617015</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.1642601504487318</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>145.96883788517155</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>61511.66007787146</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>68778.39802829869</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>2.118135942701397</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>1.118135942701397</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>1487.133848118</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.0890350755228013</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>12.275383685252352</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>1487.133848118</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>12.33091581936119</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$133,A18,'Species'!$U$2:$U$133))</x:f>
-        <x:v>18337.722293265728</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.0890350755228013</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>12.275383685252352</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>18255.13857697425</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>82.5837162914795</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0045238613743335</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.004523861374333516</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>20.26</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.707073050345508</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>50.941655007687544</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>20.26</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>51.78716335314271</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$133,A19,'Species'!$U$2:$U$133))</x:f>
-        <x:v>1049.2079295346714</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.707073050345508</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>50.941655007687544</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>1032.0779304557498</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>17.129999078921628</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.0165975829667797</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.016597582966779732</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>0.09000000000000001</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.62</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>416.8693834703355</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>0.09000000000000001</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>416.8693834703355</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$133,A20,'Species'!$U$2:$U$133))</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>37.5182445123302</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.62</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>416.8693834703355</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
-        <x:v>37.5182445123302</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>0.6343911790000001</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.2250485349513345</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>167.8991644785702</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>0.6343911790000001</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>178.52217242649664</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$133,A21,'Species'!$U$2:$U$133))</x:f>
-        <x:v>113.25289144328652</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.2250485349513345</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>167.8991644785702</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>106.51374890667509</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>6.739142536611425</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.063270165643274</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.06327016564327397</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>191.082329868</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.06</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>114.81536214968828</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>191.082329868</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>114.8153621496883</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$133,A22,'Species'!$U$2:$U$133))</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>21939.18690420062</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.06</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>114.81536214968828</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
-        <x:v>21939.18690420062</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>33.645338057000004</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.7316655633269327</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>539.0953220901055</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>33.645338057000004</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>539.3449252329892</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$133,A23,'Species'!$U$2:$U$133))</x:f>
-        <x:v>18146.442338791316</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.7316655633269327</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>539.0953220901055</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>18138.0443566689</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>8.397982122416579</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.0004630037261613</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.00046300372616129665</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>0.25</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.57</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>371.5352290971724</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>371.5352290971724</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$133,A24,'Species'!$U$2:$U$133))</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>92.8838072742931</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.57</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>371.5352290971724</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
-        <x:v>92.8838072742931</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>15.378152645999998</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>4.154491824272402</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>1427.2229619994466</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>15.378152645999998</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>1430.922385088387</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$133,A25,'Species'!$U$2:$U$133))</x:f>
-        <x:v>22004.942862467607</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>4.154491824272402</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>1427.2229619994466</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>21948.052569503747</x:v>
       </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>56.8902929638607</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.0025920428604636</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0.002592042860463543</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G25">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O25">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3854aaa120da4202"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf512a1fdd1644b3e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11783,7 +10404,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -11882,7 +10503,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>27576431.66877207</x:v>
+        <x:v>24900064.89058782</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -11896,7 +10517,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>27576431.66877207</x:v>
+        <x:v>26059454.854341455</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -11910,7 +10531,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-2676366.77818425</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -11924,7 +10545,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-1516976.8144306168</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -11935,9 +10556,9 @@
         <x:v>EEZ_622</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -11949,47 +10570,19 @@
         <x:v>EEZ_622</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_622</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_622</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6eb67771ba9448a8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R464318b5c8094800"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12036,7 +10629,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
